--- a/inspection_forms/038_uva_mlr_project_management_review_form--inspection_forms.xlsx
+++ b/inspection_forms/038_uva_mlr_project_management_review_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'on_hold',_'value':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'On Hold', 'value': 'on_hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'completed',_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Completed', 'value': 'completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'continue_project_as_is',_'value':_'continue_project_as_is'}</t>
+          <t>continue_project_as_is</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Continue project as is', 'value': 'continue_project_as_is'}</t>
+          <t>Continue project as is</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'change_project_scope',_'value':_'change_project_scope'}</t>
+          <t>change_project_scope</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Change project scope', 'value': 'change_project_scope'}</t>
+          <t>Change project scope</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'put_on_hold',_'value':_'put_on_hold'}</t>
+          <t>put_on_hold</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Put on hold', 'value': 'put_on_hold'}</t>
+          <t>Put on hold</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'terminate_project',_'value':_'terminate_project'}</t>
+          <t>terminate_project</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Terminate project', 'value': 'terminate_project'}</t>
+          <t>Terminate project</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John', 'value': 'john'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane', 'value': 'jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'joe',_'value':_'joe'}</t>
+          <t>joe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Joe', 'value': 'joe'}</t>
+          <t>Joe</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'project_manager',_'value':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Project Manager', 'value': 'project_manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_lead',_'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Lead', 'value': 'team_lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'team_member',_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Team Member', 'value': 'team_member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
